--- a/integrity_system/app/static/petition_template.xlsx
+++ b/integrity_system/app/static/petition_template.xlsx
@@ -494,7 +494,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>【信访举报导入模板】*号为必填项。组织是否采信填：是/否/空。有无影响期填：有/无/空。状态填：processing/completed/influence_period_ended。日期格式：YYYY-MM-DD</t>
+          <t>【信访举报导入模板】*号为必填项。组织是否采信填：是/否/空。有无影响期填：有/无/空。日期格式：YYYY-MM-DD</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>状态</t>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -592,11 +592,7 @@
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="J3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -632,11 +628,7 @@
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>processing</t>
-        </is>
-      </c>
+      <c r="J4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
